--- a/a1.xlsx
+++ b/a1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\TKSR PRODUCTION\job1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\tksr pv\jobapplyer\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -384,11 +384,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -607,13 +607,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="30.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" ht="15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -637,7 +637,7 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>45901</v>
       </c>
       <c r="C2" s="3" t="s">
@@ -657,7 +657,7 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="10">
         <v>45902</v>
       </c>
       <c r="C3" s="3" t="s">
@@ -677,7 +677,7 @@
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="10">
         <v>45903</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -695,7 +695,7 @@
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="10">
         <v>45904</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -715,7 +715,7 @@
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="10">
         <v>45905</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -733,7 +733,7 @@
       <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="10">
         <v>45906</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -751,7 +751,7 @@
       <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="10">
         <v>45907</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -771,7 +771,7 @@
       <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="10">
         <v>45908</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -791,7 +791,7 @@
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="10">
         <v>45909</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -809,7 +809,7 @@
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="10">
         <v>45910</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -829,7 +829,7 @@
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="10">
         <v>45911</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -849,7 +849,7 @@
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="10">
         <v>45912</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -869,7 +869,7 @@
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="10">
         <v>45913</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -887,7 +887,7 @@
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="12">
+      <c r="B15" s="10">
         <v>45914</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -905,7 +905,7 @@
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="12">
+      <c r="B16" s="10">
         <v>45915</v>
       </c>
       <c r="C16" s="8" t="s">
@@ -923,7 +923,7 @@
       <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="12">
+      <c r="B17" s="10">
         <v>45916</v>
       </c>
       <c r="C17" s="8" t="s">
@@ -943,7 +943,7 @@
       <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="10">
         <v>45917</v>
       </c>
       <c r="C18" s="8" t="s">
@@ -961,23 +961,23 @@
       <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="10">
         <v>45918</v>
       </c>
       <c r="C19" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="11"/>
+      <c r="E19" s="12"/>
       <c r="F19" s="4"/>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1">
       <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="10">
         <v>45919</v>
       </c>
       <c r="C20" s="9" t="s">
@@ -995,7 +995,7 @@
       <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="10">
         <v>45920</v>
       </c>
       <c r="C21" s="3" t="s">
@@ -1013,7 +1013,7 @@
       <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="10">
         <v>45921</v>
       </c>
       <c r="C22" s="8" t="s">
@@ -1026,6 +1026,11 @@
         <v>63</v>
       </c>
       <c r="F22" s="4"/>
+    </row>
+    <row r="23" spans="1:6" ht="15.75" customHeight="1">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
